--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C331"/>
+  <dimension ref="A1:C332"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4725,6 +4725,19 @@
         <v>515.5700000000001</v>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>399</v>
+      </c>
+      <c r="C332" t="n">
+        <v>505.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C332"/>
+  <dimension ref="A1:C333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4738,6 +4738,19 @@
         <v>505.32</v>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>399</v>
+      </c>
+      <c r="C333" t="n">
+        <v>492.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C333"/>
+  <dimension ref="A1:C334"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4751,6 +4751,19 @@
         <v>492.35</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>399</v>
+      </c>
+      <c r="C334" t="n">
+        <v>459.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C334"/>
+  <dimension ref="A1:C335"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4764,6 +4764,19 @@
         <v>459.66</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>399</v>
+      </c>
+      <c r="C335" t="n">
+        <v>457.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C335"/>
+  <dimension ref="A1:C336"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4777,6 +4777,19 @@
         <v>457.94</v>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>399</v>
+      </c>
+      <c r="C336" t="n">
+        <v>468.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C336"/>
+  <dimension ref="A1:C337"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4790,6 +4790,19 @@
         <v>468.75</v>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>399</v>
+      </c>
+      <c r="C337" t="n">
+        <v>478.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C337"/>
+  <dimension ref="A1:C338"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4803,6 +4803,19 @@
         <v>478.25</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>399</v>
+      </c>
+      <c r="C338" t="n">
+        <v>492.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C338"/>
+  <dimension ref="A1:C339"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4816,6 +4816,19 @@
         <v>492.19</v>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>399</v>
+      </c>
+      <c r="C339" t="n">
+        <v>453.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C339"/>
+  <dimension ref="A1:C340"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4829,6 +4829,19 @@
         <v>453.22</v>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>399</v>
+      </c>
+      <c r="C340" t="n">
+        <v>476.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C340"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4842,6 +4842,19 @@
         <v>476.66</v>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>399</v>
+      </c>
+      <c r="C341" t="n">
+        <v>469.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C341"/>
+  <dimension ref="A1:C342"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4855,6 +4855,19 @@
         <v>469.75</v>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>399</v>
+      </c>
+      <c r="C342" t="n">
+        <v>467.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C342"/>
+  <dimension ref="A1:C343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4868,6 +4868,19 @@
         <v>467.15</v>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>399</v>
+      </c>
+      <c r="C343" t="n">
+        <v>457.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C343"/>
+  <dimension ref="A1:C344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4881,6 +4881,19 @@
         <v>457.99</v>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>399</v>
+      </c>
+      <c r="C344" t="n">
+        <v>455.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C344"/>
+  <dimension ref="A1:C345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4894,6 +4894,19 @@
         <v>455.71</v>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>399</v>
+      </c>
+      <c r="C345" t="n">
+        <v>480.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C345"/>
+  <dimension ref="A1:C346"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4907,6 +4907,19 @@
         <v>480.69</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>399</v>
+      </c>
+      <c r="C346" t="n">
+        <v>471.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C346"/>
+  <dimension ref="A1:C347"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4920,6 +4920,19 @@
         <v>471.74</v>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>399</v>
+      </c>
+      <c r="C347" t="n">
+        <v>460.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C347"/>
+  <dimension ref="A1:C348"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4933,6 +4933,19 @@
         <v>460.33</v>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>399</v>
+      </c>
+      <c r="C348" t="n">
+        <v>451.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C348"/>
+  <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4946,6 +4946,19 @@
         <v>451.28</v>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>399</v>
+      </c>
+      <c r="C349" t="n">
+        <v>440.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C349"/>
+  <dimension ref="A1:C350"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4959,6 +4959,19 @@
         <v>440.72</v>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>399</v>
+      </c>
+      <c r="C350" t="n">
+        <v>451.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C350"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4972,6 +4972,19 @@
         <v>451.9</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>399</v>
+      </c>
+      <c r="C351" t="n">
+        <v>480.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4985,6 +4985,19 @@
         <v>480.03</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>399</v>
+      </c>
+      <c r="C352" t="n">
+        <v>475.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C352"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4998,6 +4998,19 @@
         <v>475.01</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>399</v>
+      </c>
+      <c r="C353" t="n">
+        <v>452.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C354"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5011,6 +5011,19 @@
         <v>452.23</v>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>399</v>
+      </c>
+      <c r="C354" t="n">
+        <v>442.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C354"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5024,6 +5024,19 @@
         <v>442.57</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>399</v>
+      </c>
+      <c r="C355" t="n">
+        <v>423.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C355"/>
+  <dimension ref="A1:C356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5037,6 +5037,19 @@
         <v>423.4</v>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>399</v>
+      </c>
+      <c r="C356" t="n">
+        <v>421.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C356"/>
+  <dimension ref="A1:C357"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5050,6 +5050,19 @@
         <v>421.48</v>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>399</v>
+      </c>
+      <c r="C357" t="n">
+        <v>439.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C357"/>
+  <dimension ref="A1:C358"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5063,6 +5063,19 @@
         <v>439.47</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>399</v>
+      </c>
+      <c r="C358" t="n">
+        <v>471.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C358"/>
+  <dimension ref="A1:C359"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5076,6 +5076,19 @@
         <v>471.26</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>399</v>
+      </c>
+      <c r="C359" t="n">
+        <v>487.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C359"/>
+  <dimension ref="A1:C360"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5089,6 +5089,19 @@
         <v>487.4</v>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>399</v>
+      </c>
+      <c r="C360" t="n">
+        <v>511.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C360"/>
+  <dimension ref="A1:C361"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5102,6 +5102,19 @@
         <v>511.38</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>399</v>
+      </c>
+      <c r="C361" t="n">
+        <v>471.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C361"/>
+  <dimension ref="A1:C362"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5115,6 +5115,19 @@
         <v>471.98</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>399</v>
+      </c>
+      <c r="C362" t="n">
+        <v>474.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C362"/>
+  <dimension ref="A1:C363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5128,6 +5128,19 @@
         <v>474.91</v>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>399</v>
+      </c>
+      <c r="C363" t="n">
+        <v>471.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C363"/>
+  <dimension ref="A1:C364"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5141,6 +5141,19 @@
         <v>471.88</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>399</v>
+      </c>
+      <c r="C364" t="n">
+        <v>476.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C364"/>
+  <dimension ref="A1:C365"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5154,6 +5154,19 @@
         <v>476.88</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>399</v>
+      </c>
+      <c r="C365" t="n">
+        <v>470.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C365"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5167,6 +5167,19 @@
         <v>470.12</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>399</v>
+      </c>
+      <c r="C366" t="n">
+        <v>500.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C366"/>
+  <dimension ref="A1:C367"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5180,6 +5180,19 @@
         <v>500.34</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>399</v>
+      </c>
+      <c r="C367" t="n">
+        <v>484.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C367"/>
+  <dimension ref="A1:C368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5193,6 +5193,19 @@
         <v>484.16</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>399</v>
+      </c>
+      <c r="C368" t="n">
+        <v>490.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C368"/>
+  <dimension ref="A1:C369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5206,6 +5206,19 @@
         <v>490.56</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>399</v>
+      </c>
+      <c r="C369" t="n">
+        <v>483.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C369"/>
+  <dimension ref="A1:C370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5219,6 +5219,19 @@
         <v>483.34</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>399</v>
+      </c>
+      <c r="C370" t="n">
+        <v>465.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C370"/>
+  <dimension ref="A1:C371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5232,6 +5232,19 @@
         <v>465.72</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>399</v>
+      </c>
+      <c r="C371" t="n">
+        <v>472.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C371"/>
+  <dimension ref="A1:C372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5245,6 +5245,19 @@
         <v>472.78</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>399</v>
+      </c>
+      <c r="C372" t="n">
+        <v>440.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C375"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5258,6 +5258,45 @@
         <v>440.38</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>399</v>
+      </c>
+      <c r="C373" t="n">
+        <v>454.44</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>399</v>
+      </c>
+      <c r="C374" t="n">
+        <v>470.84</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>399</v>
+      </c>
+      <c r="C375" t="n">
+        <v>462.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C375"/>
+  <dimension ref="A1:C376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5297,6 +5297,19 @@
         <v>462.62</v>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>399</v>
+      </c>
+      <c r="C376" t="n">
+        <v>447.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C376"/>
+  <dimension ref="A1:C377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5310,6 +5310,19 @@
         <v>447.75</v>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>399</v>
+      </c>
+      <c r="C377" t="n">
+        <v>443.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C377"/>
+  <dimension ref="A1:C378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5323,6 +5323,19 @@
         <v>443.41</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>399</v>
+      </c>
+      <c r="C378" t="n">
+        <v>444.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C378"/>
+  <dimension ref="A1:C379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5336,6 +5336,19 @@
         <v>444.31</v>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>399</v>
+      </c>
+      <c r="C379" t="n">
+        <v>459.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nelly_aov.xlsx
+++ b/data/nelly_aov.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C379"/>
+  <dimension ref="A1:C380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5349,6 +5349,19 @@
         <v>459.62</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>399</v>
+      </c>
+      <c r="C380" t="n">
+        <v>459.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
